--- a/Matriz Cálculo.xlsx
+++ b/Matriz Cálculo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BA29623-5819-4305-AFA6-24EF525B993C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0DD2BFD-2A0C-41D9-8449-9168FD2D1782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{253715C3-2E47-4B39-90F5-591DA4532381}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="82">
   <si>
     <r>
       <t>R</t>
@@ -820,6 +820,12 @@
       </rPr>
       <t>ftot_x</t>
     </r>
+  </si>
+  <si>
+    <t>dFx_Cir</t>
+  </si>
+  <si>
+    <t>dFy_Cir</t>
   </si>
 </sst>
 </file>
@@ -890,13 +896,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1214,21 +1220,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D1E63BF-A397-4140-831C-91F1C266FD5A}">
   <dimension ref="A1:AH40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="7" width="4.90625" hidden="1" customWidth="1"/>
-    <col min="8" max="12" width="4.90625" customWidth="1"/>
-    <col min="13" max="14" width="4.90625" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="8.08984375" hidden="1" customWidth="1"/>
-    <col min="16" max="17" width="4.90625" customWidth="1"/>
-    <col min="18" max="18" width="9" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="4.90625" customWidth="1"/>
-    <col min="21" max="21" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="4.90625" customWidth="1"/>
-    <col min="24" max="24" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="31" width="4.90625" customWidth="1"/>
-    <col min="32" max="32" width="5.26953125" customWidth="1"/>
-    <col min="33" max="38" width="4.90625" customWidth="1"/>
+    <col min="4" max="7" width="4.85546875" hidden="1" customWidth="1"/>
+    <col min="8" max="12" width="4.85546875" customWidth="1"/>
+    <col min="13" max="14" width="4.85546875" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="8.140625" hidden="1" customWidth="1"/>
+    <col min="16" max="17" width="4.85546875" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="4.85546875" customWidth="1"/>
+    <col min="21" max="21" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="4.85546875" customWidth="1"/>
+    <col min="24" max="24" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="31" width="4.85546875" customWidth="1"/>
+    <col min="32" max="32" width="5.28515625" customWidth="1"/>
+    <col min="33" max="38" width="4.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34">
@@ -1303,71 +1309,71 @@
       </c>
     </row>
     <row r="2" spans="1:34">
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="3" t="s">
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3" t="s">
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3" t="s">
+      <c r="Q2" s="7"/>
+      <c r="R2" s="7"/>
+      <c r="S2" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
-      <c r="V2" s="3" t="s">
+      <c r="T2" s="7"/>
+      <c r="U2" s="7"/>
+      <c r="V2" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="W2" s="3"/>
-      <c r="X2" s="3"/>
-      <c r="Y2" s="4"/>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
-      <c r="AB2" s="4"/>
-      <c r="AC2" s="4"/>
-      <c r="AD2" s="4"/>
-      <c r="AE2" s="4"/>
-      <c r="AF2" s="4"/>
-      <c r="AG2" s="4"/>
-      <c r="AH2" s="4"/>
-    </row>
-    <row r="3" spans="1:34" ht="16.5">
-      <c r="D3" s="3" t="s">
+      <c r="W2" s="7"/>
+      <c r="X2" s="7"/>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
+      <c r="AA2" s="3"/>
+      <c r="AB2" s="3"/>
+      <c r="AC2" s="3"/>
+      <c r="AD2" s="3"/>
+      <c r="AE2" s="3"/>
+      <c r="AF2" s="3"/>
+      <c r="AG2" s="3"/>
+      <c r="AH2" s="3"/>
+    </row>
+    <row r="3" spans="1:34" ht="18">
+      <c r="D3" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3" t="s">
+      <c r="E3" s="7"/>
+      <c r="F3" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="G3" s="3"/>
+      <c r="G3" s="7"/>
       <c r="H3" s="1"/>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3" t="s">
+      <c r="J3" s="7"/>
+      <c r="K3" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L3" s="3"/>
+      <c r="L3" s="7"/>
       <c r="M3" s="2" t="s">
         <v>36</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="O3" s="5" t="s">
+      <c r="O3" s="4" t="s">
         <v>38</v>
       </c>
       <c r="P3" s="2" t="s">
@@ -1376,7 +1382,7 @@
       <c r="Q3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="R3" s="5" t="s">
+      <c r="R3" s="4" t="s">
         <v>38</v>
       </c>
       <c r="S3" s="2" t="s">
@@ -1385,7 +1391,7 @@
       <c r="T3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="U3" s="5" t="s">
+      <c r="U3" s="4" t="s">
         <v>38</v>
       </c>
       <c r="V3" s="2" t="s">
@@ -1394,7 +1400,7 @@
       <c r="W3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="X3" s="5" t="s">
+      <c r="X3" s="4" t="s">
         <v>38</v>
       </c>
       <c r="Y3" s="2" t="s">
@@ -1409,8 +1415,8 @@
       <c r="AF3" s="2"/>
       <c r="AG3" s="2"/>
     </row>
-    <row r="4" spans="1:34" ht="16.5" hidden="1">
-      <c r="B4" s="3" t="s">
+    <row r="4" spans="1:34" ht="18" hidden="1">
+      <c r="B4" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C4" t="s">
@@ -1426,8 +1432,8 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:34" ht="16.5" hidden="1">
-      <c r="B5" s="3"/>
+    <row r="5" spans="1:34" ht="18" hidden="1">
+      <c r="B5" s="7"/>
       <c r="C5" t="s">
         <v>6</v>
       </c>
@@ -1441,8 +1447,8 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:34" ht="16.5" hidden="1">
-      <c r="B6" s="3"/>
+    <row r="6" spans="1:34" ht="18" hidden="1">
+      <c r="B6" s="7"/>
       <c r="C6" t="s">
         <v>0</v>
       </c>
@@ -1456,8 +1462,8 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:34" ht="16.5" hidden="1">
-      <c r="B7" s="3"/>
+    <row r="7" spans="1:34" ht="18" hidden="1">
+      <c r="B7" s="7"/>
       <c r="C7" t="s">
         <v>1</v>
       </c>
@@ -1472,22 +1478,22 @@
       </c>
     </row>
     <row r="8" spans="1:34" ht="16.5" hidden="1" customHeight="1">
-      <c r="B8" s="3"/>
+      <c r="B8" s="7"/>
       <c r="C8" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:34" ht="16.5" hidden="1" customHeight="1">
-      <c r="B9" s="3"/>
+      <c r="B9" s="7"/>
       <c r="C9" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:34" ht="16.5">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:34" ht="18">
+      <c r="A10" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C10" t="s">
@@ -1510,8 +1516,8 @@
       </c>
     </row>
     <row r="11" spans="1:34" ht="16.5" customHeight="1">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
       <c r="C11" t="s">
         <v>5</v>
       </c>
@@ -1531,9 +1537,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:34" ht="16.5">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
+    <row r="12" spans="1:34" ht="18">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
       <c r="C12" t="s">
         <v>2</v>
       </c>
@@ -1550,9 +1556,9 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:34" ht="16.5">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
+    <row r="13" spans="1:34" ht="18">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
       <c r="C13" t="s">
         <v>7</v>
       </c>
@@ -1569,9 +1575,9 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:34" ht="16.5">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3" t="s">
+    <row r="14" spans="1:34" ht="18">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7" t="s">
         <v>17</v>
       </c>
       <c r="C14" t="s">
@@ -1587,9 +1593,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:34" ht="16.5">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
+    <row r="15" spans="1:34" ht="18">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
       <c r="C15" t="s">
         <v>11</v>
       </c>
@@ -1604,8 +1610,8 @@
       </c>
     </row>
     <row r="16" spans="1:34" ht="16.5" customHeight="1">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
       <c r="C16" t="s">
         <v>12</v>
       </c>
@@ -1622,9 +1628,9 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:26" ht="16.5">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
+    <row r="17" spans="1:26" ht="18">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
       <c r="C17" t="s">
         <v>13</v>
       </c>
@@ -1641,9 +1647,9 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:26" ht="16.5">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3" t="s">
+    <row r="18" spans="1:26" ht="18">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7" t="s">
         <v>18</v>
       </c>
       <c r="C18" t="s">
@@ -1662,9 +1668,9 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:26" ht="16.5">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
+    <row r="19" spans="1:26" ht="18">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
       <c r="C19" t="s">
         <v>15</v>
       </c>
@@ -1681,9 +1687,9 @@
         <v>59</v>
       </c>
     </row>
-    <row r="20" spans="1:26" ht="16.5">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
+    <row r="20" spans="1:26" ht="18">
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
       <c r="C20" t="s">
         <v>16</v>
       </c>
@@ -1706,9 +1712,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:26" ht="16.5">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
+    <row r="21" spans="1:26" ht="18">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
       <c r="C21" t="s">
         <v>13</v>
       </c>
@@ -1731,9 +1737,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:26" ht="16.5">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
+    <row r="22" spans="1:26" ht="18">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
       <c r="C22" t="s">
         <v>75</v>
       </c>
@@ -1746,13 +1752,16 @@
       <c r="V22">
         <v>1</v>
       </c>
+      <c r="X22" t="s">
+        <v>80</v>
+      </c>
       <c r="Y22">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:26" ht="16.5">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
+    <row r="23" spans="1:26" ht="18">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
       <c r="C23" t="s">
         <v>75</v>
       </c>
@@ -1765,41 +1774,44 @@
       <c r="W23">
         <v>1</v>
       </c>
+      <c r="X23" t="s">
+        <v>81</v>
+      </c>
       <c r="Z23">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:26">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="6"/>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="6"/>
-      <c r="S24" s="6"/>
-      <c r="T24" s="6"/>
-      <c r="U24" s="6"/>
-      <c r="V24" s="6"/>
-      <c r="W24" s="6"/>
-      <c r="X24" s="6"/>
-    </row>
-    <row r="25" spans="1:26" ht="16.5">
-      <c r="A25" s="3" t="s">
+      <c r="A24" s="5"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="5"/>
+      <c r="R24" s="5"/>
+      <c r="S24" s="5"/>
+      <c r="T24" s="5"/>
+      <c r="U24" s="5"/>
+      <c r="V24" s="5"/>
+      <c r="W24" s="5"/>
+      <c r="X24" s="5"/>
+    </row>
+    <row r="25" spans="1:26" ht="18">
+      <c r="A25" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="7" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="2" t="s">
@@ -1812,9 +1824,9 @@
         <v>62</v>
       </c>
     </row>
-    <row r="26" spans="1:26" ht="16.5">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
+    <row r="26" spans="1:26" ht="18">
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
       <c r="C26" s="2" t="s">
         <v>27</v>
       </c>
@@ -1826,8 +1838,8 @@
       </c>
     </row>
     <row r="27" spans="1:26">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
       <c r="C27" t="s">
         <v>28</v>
       </c>
@@ -1838,9 +1850,9 @@
         <v>64</v>
       </c>
     </row>
-    <row r="28" spans="1:26" ht="16.5">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3" t="s">
+    <row r="28" spans="1:26" ht="18">
+      <c r="A28" s="7"/>
+      <c r="B28" s="7" t="s">
         <v>9</v>
       </c>
       <c r="C28" s="2" t="s">
@@ -1853,9 +1865,9 @@
         <v>66</v>
       </c>
     </row>
-    <row r="29" spans="1:26" ht="16.5">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
+    <row r="29" spans="1:26" ht="18">
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
       <c r="C29" s="2" t="s">
         <v>31</v>
       </c>
@@ -1867,8 +1879,8 @@
       </c>
     </row>
     <row r="30" spans="1:26">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
       <c r="C30" t="s">
         <v>30</v>
       </c>
@@ -1879,9 +1891,9 @@
         <v>65</v>
       </c>
     </row>
-    <row r="31" spans="1:26" ht="16.5">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3" t="s">
+    <row r="31" spans="1:26" ht="18">
+      <c r="A31" s="7"/>
+      <c r="B31" s="7" t="s">
         <v>17</v>
       </c>
       <c r="C31" s="2" t="s">
@@ -1894,9 +1906,9 @@
         <v>68</v>
       </c>
     </row>
-    <row r="32" spans="1:26" ht="16.5">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
+    <row r="32" spans="1:26" ht="18">
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
       <c r="C32" s="2" t="s">
         <v>29</v>
       </c>
@@ -1908,8 +1920,8 @@
       </c>
     </row>
     <row r="33" spans="1:24">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3"/>
+      <c r="A33" s="7"/>
+      <c r="B33" s="7"/>
       <c r="C33" t="s">
         <v>32</v>
       </c>
@@ -1920,9 +1932,9 @@
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="1:24" ht="16.5">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3" t="s">
+    <row r="34" spans="1:24" ht="18">
+      <c r="A34" s="7"/>
+      <c r="B34" s="7" t="s">
         <v>18</v>
       </c>
       <c r="C34" s="2" t="s">
@@ -1935,9 +1947,9 @@
         <v>71</v>
       </c>
     </row>
-    <row r="35" spans="1:24" ht="16.5">
-      <c r="A35" s="3"/>
-      <c r="B35" s="3"/>
+    <row r="35" spans="1:24" ht="18">
+      <c r="A35" s="7"/>
+      <c r="B35" s="7"/>
       <c r="C35" s="2" t="s">
         <v>33</v>
       </c>
@@ -1949,8 +1961,8 @@
       </c>
     </row>
     <row r="36" spans="1:24">
-      <c r="A36" s="3"/>
-      <c r="B36" s="3"/>
+      <c r="A36" s="7"/>
+      <c r="B36" s="7"/>
       <c r="C36" t="s">
         <v>34</v>
       </c>
@@ -1962,7 +1974,7 @@
       </c>
     </row>
     <row r="37" spans="1:24">
-      <c r="A37" s="3"/>
+      <c r="A37" s="7"/>
       <c r="C37" t="s">
         <v>23</v>
       </c>
@@ -1971,7 +1983,7 @@
       </c>
     </row>
     <row r="38" spans="1:24">
-      <c r="A38" s="3"/>
+      <c r="A38" s="7"/>
       <c r="C38" t="s">
         <v>24</v>
       </c>
@@ -1980,7 +1992,7 @@
       </c>
     </row>
     <row r="39" spans="1:24">
-      <c r="A39" s="3"/>
+      <c r="A39" s="7"/>
       <c r="C39" t="s">
         <v>25</v>
       </c>
@@ -1989,7 +2001,7 @@
       </c>
     </row>
     <row r="40" spans="1:24">
-      <c r="A40" s="3"/>
+      <c r="A40" s="7"/>
       <c r="C40" t="s">
         <v>26</v>
       </c>
@@ -1999,12 +2011,8 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="B18:B23"/>
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="B28:B30"/>
-    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="A10:A23"/>
+    <mergeCell ref="A25:A40"/>
     <mergeCell ref="B10:B13"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:R2"/>
@@ -2015,8 +2023,12 @@
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="B4:B9"/>
-    <mergeCell ref="A10:A23"/>
-    <mergeCell ref="A25:A40"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="B18:B23"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="B31:B33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
